--- a/outputs/019fa831-70ed-7823-bd30-ff28326f813f/2026-09-12_算数授業研究公開講座_in大阪_イベント情報.xlsx
+++ b/outputs/019fa831-70ed-7823-bd30-ff28326f813f/2026-09-12_算数授業研究公開講座_in大阪_イベント情報.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="1" r:id="R42ae927ef32f4a05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="Rcce0ea8bfc92499a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="3" r:id="R20e7f3aab07647f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="開催日" sheetId="4" r:id="R894a1e9d682a4419"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会場" sheetId="5" r:id="R1284e0e3533f4005"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セッション" sheetId="6" r:id="R30c69426609945fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プログラム項目" sheetId="7" r:id="R746934a989b2427b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="8" r:id="R95c36e2d139d4133"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="9" r:id="R8b35d7ee6fbb4eeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="10" r:id="R8eb4b213744d42d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="11" r:id="R444014f182674fe7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="1" r:id="R81ce46eefbd94c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R58b7368604bb44f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="3" r:id="Rfa2d017725484b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="開催日" sheetId="4" r:id="R72f9809f24104f9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会場" sheetId="5" r:id="R9c17aa70d5e741a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セッション" sheetId="6" r:id="R4f86648805504641"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プログラム項目" sheetId="7" r:id="R767b3e16de0541c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="8" r:id="R45e370141a694cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="9" r:id="R284f2e5cfdfb4451"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="10" r:id="R6a5528a459694225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="11" r:id="R871419c5310d481b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -401,7 +401,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="ＭＳ ゴシック"/>
         <x:family val="3"/>
       </x:rPr>
@@ -409,7 +410,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Carlito"/>
         <x:family val="2"/>
       </x:rPr>
@@ -417,7 +419,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="ＭＳ ゴシック"/>
         <x:family val="3"/>
       </x:rPr>
@@ -425,7 +428,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Carlito"/>
         <x:family val="2"/>
       </x:rPr>
@@ -474,7 +478,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="ＭＳ Ｐゴシック"/>
         <x:family val="2"/>
       </x:rPr>
@@ -482,7 +487,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Carlito"/>
         <x:family val="2"/>
       </x:rPr>
@@ -490,7 +496,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="ＭＳ ゴシック"/>
         <x:family val="3"/>
       </x:rPr>
@@ -568,9 +575,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">補助ブランド色</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">#85C44F</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">brandColor2。# + 6桁16進</x:t>
@@ -1993,141 +1997,141 @@
   <x:sheetData>
     <x:row r="1" ht="27.950000762939453" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="79.1500015258789" customHeight="1">
       <x:c r="A4" s="5" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="B4" s="5" t="s">
+      <x:c r="C4" s="5" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s">
-        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="6" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="s">
+      <x:c r="C5" s="6" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="6" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>235</x:v>
-      </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="39.599998474121094" customHeight="1">
       <x:c r="A7" s="6" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>237</x:v>
-      </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26.450000762939453" customHeight="1">
       <x:c r="A8" s="6" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="s">
-        <x:v>239</x:v>
-      </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="39.599998474121094" customHeight="1">
       <x:c r="A9" s="6" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>241</x:v>
-      </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="26.450000762939453" customHeight="1">
       <x:c r="A10" s="6" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="s">
-        <x:v>243</x:v>
-      </x:c>
       <x:c r="C10" s="6" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="39.599998474121094" customHeight="1">
       <x:c r="A11" s="6" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="s">
-        <x:v>245</x:v>
-      </x:c>
       <x:c r="C11" s="6" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" customHeight="1">
       <x:c r="A12" s="6" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="B12" s="6" t="s">
-        <x:v>247</x:v>
-      </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="39.599998474121094" customHeight="1">
       <x:c r="A13" s="6" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="B13" s="6" t="s">
-        <x:v>249</x:v>
-      </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="26.450000762939453" customHeight="1">
       <x:c r="A14" s="6" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="B14" s="6" t="s">
-        <x:v>251</x:v>
-      </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2200,7 +2204,7 @@
   <x:sheetData>
     <x:row r="1" ht="27.950000762939453" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
@@ -2209,36 +2213,36 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="C3" s="1" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="E3" s="1" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="39.599998474121094" customHeight="1">
       <x:c r="A4" s="5" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="B4" s="5" t="s">
+      <x:c r="C4" s="5" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="s">
+      <x:c r="D4" s="5" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="D4" s="5" t="s">
+      <x:c r="E4" s="5" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -2255,7 +2259,7 @@
         <x:v>申込ページに掲載されている表示URLを採用し、資料リンクへ追加した。</x:v>
       </x:c>
       <x:c r="E5" s="21" t="str">
-        <x:v>採用URL：https://maps.app.goo.gl/tZbbaXNo8fm7tuFm7</x:v>
+        <x:v>採用URL：https://maps.app.goo.gl/bb6P77Zxr3NpJnTQA</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2640,8 +2644,8 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2961478ecc1439f"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b1169686bcd4cb4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe46cf8f205b4479"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8315ac1af66046fb"/>
 </x:worksheet>
 </file>
 
@@ -2871,118 +2875,118 @@
       <x:c r="A18" s="3" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B18" s="6" t="s">
-        <x:v>110</x:v>
+      <x:c r="B18" s="6" t="str">
+        <x:v>#002F6C</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" customHeight="1">
       <x:c r="A19" s="3" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B19" s="18" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="B19" s="18" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" customHeight="1">
       <x:c r="A20" s="3" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="B20" s="6" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" customHeight="1">
       <x:c r="A21" s="3" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="B21" s="6" t="s">
-        <x:v>119</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="39.599998474121094" customHeight="1">
       <x:c r="A22" s="3" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B22" s="6" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" customHeight="1">
       <x:c r="A23" s="3" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B23" s="6"/>
       <x:c r="C23" s="3" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" customHeight="1">
       <x:c r="A24" s="3" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B24" s="6"/>
       <x:c r="C24" s="3" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" customHeight="1">
       <x:c r="A25" s="3" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B25" s="6"/>
       <x:c r="C25" s="3" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B26" s="7"/>
       <x:c r="C26" s="4" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3010,7 +3014,7 @@
   <x:sheetData>
     <x:row r="1" ht="27.950000762939453" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
@@ -3019,36 +3023,36 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="C3" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="E3" s="1" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="5" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B4" s="5" t="s">
+      <x:c r="C4" s="5" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
+      <x:c r="E4" s="5" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3133,8 +3137,8 @@
     <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0714e84284164561"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3339f9706c045fe"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf14d89eea5a742b3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2bce675994840da"/>
 </x:worksheet>
 </file>
 
@@ -3149,20 +3153,20 @@
   <x:sheetData>
     <x:row r="1" ht="27.950000762939453" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="C3" s="1" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3275,8 +3279,8 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R686eaee4256e4922"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref1ec47f095e4a16"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re05a9bf66a27470c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa6ac59143be4725"/>
 </x:worksheet>
 </file>
 
@@ -3293,7 +3297,7 @@
   <x:sheetData>
     <x:row r="1" ht="27.950000762939453" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
@@ -3304,182 +3308,182 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="E3" s="1" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
+      <x:c r="F3" s="1" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="F3" s="1" t="s">
+      <x:c r="G3" s="1" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="5" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s">
-        <x:v>154</x:v>
       </x:c>
       <x:c r="D4" s="5"/>
       <x:c r="E4" s="5" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F4" s="5" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="F4" s="5" t="s">
-        <x:v>156</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="6" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
+      <x:c r="D5" s="6" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="D5" s="6" t="s">
+      <x:c r="E5" s="19" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="E5" s="19" t="s">
+      <x:c r="F5" s="6" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="F5" s="6" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="G5" s="6"/>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="6" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
+      <x:c r="D6" s="6" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="D6" s="6" t="s">
+      <x:c r="E6" s="6" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="E6" s="6" t="s">
+      <x:c r="F6" s="6" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="F6" s="6" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="G6" s="6"/>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s">
+      <x:c r="D7" s="6" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="s">
+      <x:c r="E7" s="6" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="s">
+      <x:c r="F7" s="6" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="F7" s="6" t="s">
-        <x:v>171</x:v>
       </x:c>
       <x:c r="G7" s="6"/>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C8" s="6" t="s">
+      <x:c r="D8" s="6" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="s">
+      <x:c r="E8" s="6" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="E8" s="6" t="s">
-        <x:v>175</x:v>
       </x:c>
       <x:c r="F8" s="6"/>
       <x:c r="G8" s="6"/>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
       <x:c r="A9" s="6" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="s">
+      <x:c r="D9" s="6" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="s">
+      <x:c r="E9" s="6" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6"/>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="6" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C10" s="6" t="s">
+      <x:c r="D10" s="6" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="s">
+      <x:c r="E10" s="6" t="s">
         <x:v>182</x:v>
-      </x:c>
-      <x:c r="E10" s="6" t="s">
-        <x:v>183</x:v>
       </x:c>
       <x:c r="F10" s="6"/>
       <x:c r="G10" s="6"/>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C11" s="6" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D11" s="6"/>
       <x:c r="E11" s="6" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="s">
         <x:v>185</x:v>
-      </x:c>
-      <x:c r="F11" s="6" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="G11" s="6"/>
     </x:row>
@@ -3866,8 +3870,8 @@
     <x:mergeCell ref="A1:G1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb153b0bb33749f1"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc94a8cfc065143e5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re71ce70a7bba42be"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd85afa56771f4a17"/>
 </x:worksheet>
 </file>
 
@@ -3885,7 +3889,7 @@
   <x:sheetData>
     <x:row r="1" ht="27.950000762939453" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
@@ -3895,133 +3899,133 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="E3" s="1" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
+      <x:c r="F3" s="1" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B4" s="5">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="5"/>
       <x:c r="D4" s="5" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="E4" s="5" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="F4" s="5"/>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B5" s="6">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="6"/>
       <x:c r="D5" s="6" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="E5" s="6" t="s">
-        <x:v>195</x:v>
       </x:c>
       <x:c r="F5" s="6"/>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B6" s="6">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="6"/>
       <x:c r="D6" s="6" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="s">
         <x:v>196</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="s">
-        <x:v>197</x:v>
       </x:c>
       <x:c r="F6" s="6"/>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B7" s="6">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="6"/>
       <x:c r="D7" s="6" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="E7" s="6" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="F7" s="6"/>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B8" s="6">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="6"/>
       <x:c r="D8" s="6" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="s">
         <x:v>200</x:v>
-      </x:c>
-      <x:c r="E8" s="6" t="s">
-        <x:v>201</x:v>
       </x:c>
       <x:c r="F8" s="6"/>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B9" s="6">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="6"/>
       <x:c r="D9" s="6" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="s">
-        <x:v>203</x:v>
       </x:c>
       <x:c r="F9" s="6"/>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="6" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B10" s="6">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="6"/>
       <x:c r="D10" s="6" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="E10" s="6" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="F10" s="6"/>
     </x:row>
@@ -4779,8 +4783,8 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7da68f4b66204a9d"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97ef1fef614b4224"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra12244131088463e"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3063b51323ae4178"/>
 </x:worksheet>
 </file>
 
@@ -4796,7 +4800,7 @@
   <x:sheetData>
     <x:row r="1" ht="27.950000762939453" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
@@ -4807,24 +4811,24 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26.450000762939453" customHeight="1">
       <x:c r="A4" s="5" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="B4" s="5" t="s">
+      <x:c r="C4" s="5" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s">
-        <x:v>212</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
         <x:v>63</x:v>
@@ -4832,16 +4836,16 @@
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="6" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="s">
+      <x:c r="C5" s="6" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="C5" s="6" t="s">
+      <x:c r="D5" s="6" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="s">
-        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -4855,7 +4859,7 @@
         <x:v>八尾市立志紀小学校の所在地をGoogleマップで確認できます。</x:v>
       </x:c>
       <x:c r="D6" s="21" t="str">
-        <x:v>https://maps.app.goo.gl/tZbbaXNo8fm7tuFm7</x:v>
+        <x:v>https://maps.app.goo.gl/bb6P77Zxr3NpJnTQA</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5047,7 +5051,7 @@
   <x:sheetData>
     <x:row r="1" ht="27.950000762939453" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>217</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
@@ -5058,25 +5062,25 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="C3" s="1" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="E3" s="1" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
+      <x:c r="F3" s="1" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F3" s="1" t="s">
+      <x:c r="G3" s="1" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="79.19999694824219" hidden="0" customHeight="1">
